--- a/public/templates/Inventory_Import_Template.xlsx
+++ b/public/templates/Inventory_Import_Template.xlsx
@@ -397,117 +397,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:W3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>No</v>
+        <v>Warehouse</v>
       </c>
       <c r="B1" t="str">
+        <v>Product Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>SKU (Optional)</v>
+      </c>
+      <c r="D1" t="str">
         <v>Product Code (Optional)</v>
       </c>
-      <c r="C1" t="str">
-        <v>SKU</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Product Name (Optional)</v>
-      </c>
       <c r="E1" t="str">
+        <v>Category (Optional)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Business Unit (Optional)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Supplier (Optional)</v>
+      </c>
+      <c r="H1" t="str">
         <v>UOM (Optional)</v>
       </c>
-      <c r="F1" t="str">
-        <v>Batch Number (Optional)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Expiry Date</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Team (Optional)</v>
-      </c>
       <c r="I1" t="str">
+        <v>Must Sale (Optional)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Batch Number</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Expiry Date (YYYY-MM-DD)</v>
+      </c>
+      <c r="L1" t="str">
         <v>Physical Qty</v>
       </c>
-      <c r="J1" t="str">
-        <v>Block Qty</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Returned Qty</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Sample Qty</v>
-      </c>
       <c r="M1" t="str">
-        <v>FOC Qty</v>
+        <v>COGS / Cost Price (MMK)</v>
       </c>
       <c r="N1" t="str">
-        <v>Available Qty (Optional)</v>
+        <v>Selling Price (MMK)</v>
       </c>
       <c r="O1" t="str">
-        <v>Warehouse</v>
+        <v>Category Group (Optional)</v>
       </c>
       <c r="P1" t="str">
-        <v>Branch (Optional)</v>
+        <v>Manufacturing Date (Optional)</v>
       </c>
       <c r="Q1" t="str">
-        <v>Batch Status (Optional)</v>
+        <v>Generic Name (Optional)</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Brand Name (Optional)</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Dosage Form (Optional)</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Damage Qty (Optional)</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Sample Qty (Optional)</v>
+      </c>
+      <c r="V1" t="str">
+        <v>FOC Qty (Optional)</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Notes (Optional)</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>Yangon Main Warehouse</v>
       </c>
       <c r="B2" t="str">
+        <v>Amoxicillin 500mg</v>
+      </c>
+      <c r="C2" t="str">
+        <v>AMOX-500</v>
+      </c>
+      <c r="D2" t="str">
         <v>PRD-001</v>
       </c>
-      <c r="C2" t="str">
-        <v>SKU-1001</v>
-      </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Box</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J2" t="str">
+        <v>B-2026-10-A</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-10-31</v>
+      </c>
+      <c r="L2">
+        <v>500</v>
+      </c>
+      <c r="M2">
+        <v>4000</v>
+      </c>
+      <c r="N2">
+        <v>6000</v>
+      </c>
+      <c r="O2" t="str">
+        <v>CPD</v>
+      </c>
+      <c r="P2" t="str">
+        <v>2024-10-01</v>
+      </c>
+      <c r="Q2" t="str">
         <v>Amoxicillin</v>
       </c>
-      <c r="E2" t="str">
+      <c r="R2" t="str">
+        <v>Amoxil</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Capsule</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>10</v>
+      </c>
+      <c r="V2">
+        <v>20</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Initial batch stock received</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Yangon Main Warehouse</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Paracetamol 500mg</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PARA-500</v>
+      </c>
+      <c r="D3" t="str">
+        <v>PRD-002</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mega Life</v>
+      </c>
+      <c r="H3" t="str">
         <v>Box</v>
       </c>
-      <c r="F2" t="str">
-        <v>B-2026-07-A</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2027-12-31</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Team A</v>
-      </c>
-      <c r="I2">
-        <v>500</v>
-      </c>
-      <c r="J2">
+      <c r="I3" t="str">
+        <v>No</v>
+      </c>
+      <c r="J3" t="str">
+        <v>B-2027-02-B</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2027-02-28</v>
+      </c>
+      <c r="L3">
+        <v>1000</v>
+      </c>
+      <c r="M3">
+        <v>1200</v>
+      </c>
+      <c r="N3">
+        <v>1800</v>
+      </c>
+      <c r="O3" t="str">
+        <v>G1</v>
+      </c>
+      <c r="P3" t="str">
+        <v>2025-02-01</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Paracetamol</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Panadol</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
         <v>50</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>450</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Yangon Warehouse</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Yangon</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>ACTIVE</v>
+      <c r="W3" t="str">
+        <v>Regular monthly supply</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W3"/>
   </ignoredErrors>
 </worksheet>
 </file>